--- a/labeled/Add_Eating/July/multi_seed_results/seed_606/predictions.xlsx
+++ b/labeled/Add_Eating/July/multi_seed_results/seed_606/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B146"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,1162 +442,746 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>39.5</v>
+        <v>42.09999847412109</v>
       </c>
       <c r="B2" t="n">
-        <v>44.42737579345703</v>
+        <v>36.77890396118164</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9.027777671813965</v>
+        <v>16.35651397705078</v>
       </c>
       <c r="B3" t="n">
-        <v>7.667564868927002</v>
+        <v>14.3313570022583</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23.80952453613281</v>
+        <v>18.84920692443848</v>
       </c>
       <c r="B4" t="n">
-        <v>19.27949333190918</v>
+        <v>85.77748870849609</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79.36508178710938</v>
+        <v>6.646825313568115</v>
       </c>
       <c r="B5" t="n">
-        <v>74.95314025878906</v>
+        <v>54.07943344116211</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>29.79999923706055</v>
+        <v>12.30158710479736</v>
       </c>
       <c r="B6" t="n">
-        <v>25.72258758544922</v>
+        <v>17.30401611328125</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>40</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="B7" t="n">
-        <v>27.27107429504395</v>
+        <v>7.498513698577881</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>12.32741641998291</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="B8" t="n">
-        <v>17.52112579345703</v>
+        <v>24.63302612304688</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>14.58333301544189</v>
+        <v>22.09523773193359</v>
       </c>
       <c r="B9" t="n">
-        <v>12.36729049682617</v>
+        <v>18.30945777893066</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>19.84127044677734</v>
+        <v>57.20000076293945</v>
       </c>
       <c r="B10" t="n">
-        <v>14.38511085510254</v>
+        <v>65.29977416992188</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>29.10000038146973</v>
+        <v>8.952381134033203</v>
       </c>
       <c r="B11" t="n">
-        <v>25.58002090454102</v>
+        <v>18.61176109313965</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>59.70000076293945</v>
+        <v>9.06403923034668</v>
       </c>
       <c r="B12" t="n">
-        <v>40.07402801513672</v>
+        <v>13.19377708435059</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>22.09523773193359</v>
+        <v>23</v>
       </c>
       <c r="B13" t="n">
-        <v>28.0616283416748</v>
+        <v>30.23285865783691</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11.11111068725586</v>
+        <v>9.990205764770508</v>
       </c>
       <c r="B14" t="n">
-        <v>9.957977294921875</v>
+        <v>17.72241592407227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>38.09999847412109</v>
+        <v>6.660137176513672</v>
       </c>
       <c r="B15" t="n">
-        <v>36.99701309204102</v>
+        <v>28.31354522705078</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>160.1999969482422</v>
+        <v>42.99706268310547</v>
       </c>
       <c r="B16" t="n">
-        <v>171.4323120117188</v>
+        <v>42.56198501586914</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>36.63075256347656</v>
+        <v>20.27424049377441</v>
       </c>
       <c r="B17" t="n">
-        <v>32.69325256347656</v>
+        <v>26.49592971801758</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97.94319152832031</v>
+        <v>2.938295841217041</v>
       </c>
       <c r="B18" t="n">
-        <v>95.13790130615234</v>
+        <v>9.152237892150879</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2.938295841217041</v>
+        <v>60</v>
       </c>
       <c r="B19" t="n">
-        <v>10.63870239257812</v>
+        <v>57.27074813842773</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>25.39682579040527</v>
+        <v>23.60000038146973</v>
       </c>
       <c r="B20" t="n">
-        <v>17.59199905395508</v>
+        <v>14.72103786468506</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>25.46523094177246</v>
+        <v>22.9187068939209</v>
       </c>
       <c r="B21" t="n">
-        <v>24.62172317504883</v>
+        <v>14.69087886810303</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16.38095283508301</v>
+        <v>11.50793647766113</v>
       </c>
       <c r="B22" t="n">
-        <v>21.08836936950684</v>
+        <v>17.71158981323242</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>39.17727661132812</v>
+        <v>17.46031761169434</v>
       </c>
       <c r="B23" t="n">
-        <v>34.99001312255859</v>
+        <v>17.98110198974609</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14.19999980926514</v>
+        <v>23.5</v>
       </c>
       <c r="B24" t="n">
-        <v>16.80158996582031</v>
+        <v>26.28902626037598</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>19.64285659790039</v>
+        <v>1.762977480888367</v>
       </c>
       <c r="B25" t="n">
-        <v>18.13755989074707</v>
+        <v>11.62423229217529</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>46.70000076293945</v>
+        <v>8.227228164672852</v>
       </c>
       <c r="B26" t="n">
-        <v>32.38113784790039</v>
+        <v>11.32160186767578</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>40.20000076293945</v>
+        <v>23.60000038146973</v>
       </c>
       <c r="B27" t="n">
-        <v>28.20404052734375</v>
+        <v>21.52900886535645</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>34.09999847412109</v>
+        <v>6.94444465637207</v>
       </c>
       <c r="B28" t="n">
-        <v>32.81975936889648</v>
+        <v>13.23415279388428</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>57.14285659790039</v>
+        <v>27.23809432983398</v>
       </c>
       <c r="B29" t="n">
-        <v>53.95368957519531</v>
+        <v>20.12849044799805</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103.8000030517578</v>
+        <v>129.3000030517578</v>
       </c>
       <c r="B30" t="n">
-        <v>97.50599670410156</v>
+        <v>21.06521415710449</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>19.84127044677734</v>
+        <v>40.47618865966797</v>
       </c>
       <c r="B31" t="n">
-        <v>37.15512084960938</v>
+        <v>18.88397216796875</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>34.70000076293945</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="B32" t="n">
-        <v>25.81348419189453</v>
+        <v>42.96482467651367</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>34.37805938720703</v>
+        <v>9.162561416625977</v>
       </c>
       <c r="B33" t="n">
-        <v>30.2902774810791</v>
+        <v>8.374231338500977</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>18.84920692443848</v>
+        <v>25.46523094177246</v>
       </c>
       <c r="B34" t="n">
-        <v>17.13562965393066</v>
+        <v>24.4649715423584</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>28.40352630615234</v>
+        <v>57.09999847412109</v>
       </c>
       <c r="B35" t="n">
-        <v>31.04477500915527</v>
+        <v>50.5460319519043</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>36.29999923706055</v>
+        <v>10.4761905670166</v>
       </c>
       <c r="B36" t="n">
-        <v>36.97764205932617</v>
+        <v>19.14818572998047</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121.9246063232422</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="B37" t="n">
-        <v>100.2175750732422</v>
+        <v>24.3215389251709</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>63.17335891723633</v>
+        <v>29.39999961853027</v>
       </c>
       <c r="B38" t="n">
-        <v>59.45777893066406</v>
+        <v>41.24579238891602</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>12.30158710479736</v>
+        <v>33.39862823486328</v>
       </c>
       <c r="B39" t="n">
-        <v>12.22831916809082</v>
+        <v>24.27119255065918</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>20.37218475341797</v>
+        <v>25.09920692443848</v>
       </c>
       <c r="B40" t="n">
-        <v>19.14978218078613</v>
+        <v>26.86890411376953</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>59.40000152587891</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="B41" t="n">
-        <v>58.70045852661133</v>
+        <v>29.78080368041992</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>40.09523773193359</v>
+        <v>40.45053863525391</v>
       </c>
       <c r="B42" t="n">
-        <v>25.37488746643066</v>
+        <v>37.09920501708984</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>53.20000076293945</v>
+        <v>21.23809432983398</v>
       </c>
       <c r="B43" t="n">
-        <v>52.33889007568359</v>
+        <v>20.07809829711914</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>69.63761138916016</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="B44" t="n">
-        <v>65.35403442382812</v>
+        <v>29.10832595825195</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>32.24206161499023</v>
+        <v>80.69999694824219</v>
       </c>
       <c r="B45" t="n">
-        <v>28.27090072631836</v>
+        <v>77.36839294433594</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>78.35455322265625</v>
+        <v>44.57143020629883</v>
       </c>
       <c r="B46" t="n">
-        <v>81.45429229736328</v>
+        <v>40.87978744506836</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>40.47618865966797</v>
+        <v>68.28571319580078</v>
       </c>
       <c r="B47" t="n">
-        <v>24.42657089233398</v>
+        <v>83.40571594238281</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>39.68254089355469</v>
+        <v>45.40000152587891</v>
       </c>
       <c r="B48" t="n">
-        <v>38.74117279052734</v>
+        <v>45.25623321533203</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>20.73412704467773</v>
+        <v>12.54940700531006</v>
       </c>
       <c r="B49" t="n">
-        <v>18.33416938781738</v>
+        <v>18.78054809570312</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>11.65524005889893</v>
+        <v>51.90989303588867</v>
       </c>
       <c r="B50" t="n">
-        <v>14.15063667297363</v>
+        <v>35.1678352355957</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>39.5</v>
+        <v>10.7619047164917</v>
       </c>
       <c r="B51" t="n">
-        <v>44.42737579345703</v>
+        <v>13.5545768737793</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>24.38785552978516</v>
+        <v>17.94871711730957</v>
       </c>
       <c r="B52" t="n">
-        <v>24.63144493103027</v>
+        <v>13.64698028564453</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>38.39373016357422</v>
+        <v>20.47012710571289</v>
       </c>
       <c r="B53" t="n">
-        <v>50.89555740356445</v>
+        <v>22.98357963562012</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>63.0476188659668</v>
+        <v>27.81586647033691</v>
       </c>
       <c r="B54" t="n">
-        <v>56.6494255065918</v>
+        <v>23.64077377319336</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>39.78174591064453</v>
+        <v>16.56746101379395</v>
       </c>
       <c r="B55" t="n">
-        <v>40.14419555664062</v>
+        <v>13.91348552703857</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>26.09127044677734</v>
+        <v>10.77075099945068</v>
       </c>
       <c r="B56" t="n">
-        <v>13.90303039550781</v>
+        <v>15.6358003616333</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>92.90000152587891</v>
+        <v>50.40000152587891</v>
       </c>
       <c r="B57" t="n">
-        <v>84.33014678955078</v>
+        <v>51.29312896728516</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>100</v>
+        <v>38.40000152587891</v>
       </c>
       <c r="B58" t="n">
-        <v>85.72500610351562</v>
+        <v>37.91344833374023</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>59.52381134033203</v>
+        <v>9.556650161743164</v>
       </c>
       <c r="B59" t="n">
-        <v>34.27991485595703</v>
+        <v>10.45906734466553</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>46.20000076293945</v>
+        <v>12.74703598022461</v>
       </c>
       <c r="B60" t="n">
-        <v>39.38594818115234</v>
+        <v>17.31149482727051</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>22.33104705810547</v>
+        <v>18.65079307556152</v>
       </c>
       <c r="B61" t="n">
-        <v>15.68739318847656</v>
+        <v>18.17150115966797</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>91.5</v>
+        <v>31.29999923706055</v>
       </c>
       <c r="B62" t="n">
-        <v>83.57204437255859</v>
+        <v>39.30025863647461</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>8.380952835083008</v>
+        <v>23.5238094329834</v>
       </c>
       <c r="B63" t="n">
-        <v>37.6559944152832</v>
+        <v>12.48702144622803</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>16.39999961853027</v>
+        <v>8.630952835083008</v>
       </c>
       <c r="B64" t="n">
-        <v>15.94656372070312</v>
+        <v>11.38025188446045</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>27.18253898620605</v>
+        <v>45</v>
       </c>
       <c r="B65" t="n">
-        <v>19.47537231445312</v>
+        <v>46.62298202514648</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>100</v>
+        <v>90.19999694824219</v>
       </c>
       <c r="B66" t="n">
-        <v>92.17674255371094</v>
+        <v>107.0532760620117</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>16.38095283508301</v>
+        <v>22.70000076293945</v>
       </c>
       <c r="B67" t="n">
-        <v>21.08836936950684</v>
+        <v>22.71624946594238</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>15.083251953125</v>
+        <v>12.69999980926514</v>
       </c>
       <c r="B68" t="n">
-        <v>16.16545104980469</v>
+        <v>26.76900482177734</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>39.29999923706055</v>
+        <v>21.29999923706055</v>
       </c>
       <c r="B69" t="n">
-        <v>31.49548149108887</v>
+        <v>15.46401214599609</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>26.10000038146973</v>
+        <v>13.2380952835083</v>
       </c>
       <c r="B70" t="n">
-        <v>21.51993560791016</v>
+        <v>16.55581474304199</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3.428011655807495</v>
+        <v>25.5238094329834</v>
       </c>
       <c r="B71" t="n">
-        <v>12.37387657165527</v>
+        <v>26.12230110168457</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>20.83333396911621</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="B72" t="n">
-        <v>16.89054870605469</v>
+        <v>27.72308921813965</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>46.5</v>
+        <v>16.5714282989502</v>
       </c>
       <c r="B73" t="n">
-        <v>43.72493743896484</v>
+        <v>18.44670295715332</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>13.80998992919922</v>
+        <v>24.87757110595703</v>
       </c>
       <c r="B74" t="n">
-        <v>14.52463340759277</v>
+        <v>26.50630187988281</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>7.783251285552979</v>
+        <v>10.85714244842529</v>
       </c>
       <c r="B75" t="n">
-        <v>10.75499534606934</v>
+        <v>14.64317035675049</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>27.18253898620605</v>
+        <v>8.952381134033203</v>
       </c>
       <c r="B76" t="n">
-        <v>19.47537231445312</v>
+        <v>14.63323879241943</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>79.36508178710938</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="B77" t="n">
-        <v>66.48384094238281</v>
+        <v>16.12581443786621</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>18.70000076293945</v>
+        <v>25.5</v>
       </c>
       <c r="B78" t="n">
-        <v>16.64819717407227</v>
+        <v>30.35733795166016</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>9.990205764770508</v>
+        <v>9.683794021606445</v>
       </c>
       <c r="B79" t="n">
-        <v>7.583856582641602</v>
+        <v>17.82212829589844</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>11.56126499176025</v>
+        <v>13.32027435302734</v>
       </c>
       <c r="B80" t="n">
-        <v>17.20141410827637</v>
+        <v>14.90209197998047</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2.154750347137451</v>
+        <v>2.644466161727905</v>
       </c>
       <c r="B81" t="n">
-        <v>6.525417804718018</v>
+        <v>11.64406394958496</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>14.22924900054932</v>
+        <v>5.320197105407715</v>
       </c>
       <c r="B82" t="n">
-        <v>12.40899848937988</v>
+        <v>23.82752227783203</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>59.70000076293945</v>
+        <v>25.79365158081055</v>
       </c>
       <c r="B83" t="n">
-        <v>40.07402801513672</v>
+        <v>21.95839691162109</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>6.646825313568115</v>
+        <v>141.6000061035156</v>
       </c>
       <c r="B84" t="n">
-        <v>5.167343139648438</v>
+        <v>134.7568664550781</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>30.55827713012695</v>
+        <v>19.09892272949219</v>
       </c>
       <c r="B85" t="n">
-        <v>19.81521606445312</v>
+        <v>22.52385520935059</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>32.85714340209961</v>
+        <v>14.20176315307617</v>
       </c>
       <c r="B86" t="n">
-        <v>25.45587539672852</v>
+        <v>17.31778907775879</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>22.09523773193359</v>
+        <v>10.91269874572754</v>
       </c>
       <c r="B87" t="n">
-        <v>23.32808876037598</v>
+        <v>15.11300563812256</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>8.952381134033203</v>
+        <v>32.41919708251953</v>
       </c>
       <c r="B88" t="n">
-        <v>9.760499954223633</v>
+        <v>27.23455810546875</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>9.990205764770508</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="B89" t="n">
-        <v>7.583856582641602</v>
+        <v>20.87843132019043</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>39.09999847412109</v>
+        <v>18.4761905670166</v>
       </c>
       <c r="B90" t="n">
-        <v>37.00836181640625</v>
+        <v>22.71152687072754</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>20.27424049377441</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="B91" t="n">
-        <v>24.94978713989258</v>
+        <v>23.80098533630371</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>26.40394020080566</v>
+        <v>29.90476226806641</v>
       </c>
       <c r="B92" t="n">
-        <v>20.01004791259766</v>
+        <v>22.50746726989746</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>41.20000076293945</v>
+        <v>22.5</v>
       </c>
       <c r="B93" t="n">
-        <v>37.37318420410156</v>
+        <v>16.96710395812988</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>17.26190567016602</v>
+        <v>20.53571510314941</v>
       </c>
       <c r="B94" t="n">
-        <v>22.65364456176758</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>22.9187068939209</v>
-      </c>
-      <c r="B95" t="n">
-        <v>20.05018043518066</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>11.50793647766113</v>
-      </c>
-      <c r="B96" t="n">
-        <v>9.461183547973633</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>17.46031761169434</v>
-      </c>
-      <c r="B97" t="n">
-        <v>14.01067161560059</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>1.762977480888367</v>
-      </c>
-      <c r="B98" t="n">
-        <v>9.080656051635742</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>8.227228164672852</v>
-      </c>
-      <c r="B99" t="n">
-        <v>9.787870407104492</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>80.69999694824219</v>
-      </c>
-      <c r="B100" t="n">
-        <v>73.23861694335938</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>27.23809432983398</v>
-      </c>
-      <c r="B101" t="n">
-        <v>16.13560485839844</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>129.3000030517578</v>
-      </c>
-      <c r="B102" t="n">
-        <v>123.4492263793945</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>40.47618865966797</v>
-      </c>
-      <c r="B103" t="n">
-        <v>24.42657089233398</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>44.70000076293945</v>
-      </c>
-      <c r="B104" t="n">
-        <v>42.43708419799805</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>9.162561416625977</v>
-      </c>
-      <c r="B105" t="n">
-        <v>5.901192665100098</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>25.46523094177246</v>
-      </c>
-      <c r="B106" t="n">
-        <v>24.62172317504883</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>57.09999847412109</v>
-      </c>
-      <c r="B107" t="n">
-        <v>51.01537322998047</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>10.4761905670166</v>
-      </c>
-      <c r="B108" t="n">
-        <v>30.4447021484375</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>29.39999961853027</v>
-      </c>
-      <c r="B109" t="n">
-        <v>28.6807804107666</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>26.15083312988281</v>
-      </c>
-      <c r="B110" t="n">
-        <v>24.93844985961914</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>43.79999923706055</v>
-      </c>
-      <c r="B111" t="n">
-        <v>43.02583694458008</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>17.94871711730957</v>
-      </c>
-      <c r="B112" t="n">
-        <v>14.16029930114746</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>44.57143020629883</v>
-      </c>
-      <c r="B113" t="n">
-        <v>43.3536262512207</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>17.10000038146973</v>
-      </c>
-      <c r="B114" t="n">
-        <v>13.80988121032715</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>12.54940700531006</v>
-      </c>
-      <c r="B115" t="n">
-        <v>12.48494148254395</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>13.32027435302734</v>
-      </c>
-      <c r="B116" t="n">
-        <v>15.87123680114746</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>21.82539749145508</v>
-      </c>
-      <c r="B117" t="n">
-        <v>21.85883140563965</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>7.242063522338867</v>
-      </c>
-      <c r="B118" t="n">
-        <v>5.348680019378662</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>27.81586647033691</v>
-      </c>
-      <c r="B119" t="n">
-        <v>32.35894393920898</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>16.56746101379395</v>
-      </c>
-      <c r="B120" t="n">
-        <v>9.334451675415039</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>10.77075099945068</v>
-      </c>
-      <c r="B121" t="n">
-        <v>8.343494415283203</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>36.23898315429688</v>
-      </c>
-      <c r="B122" t="n">
-        <v>38.55529403686523</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>16.96428489685059</v>
-      </c>
-      <c r="B123" t="n">
-        <v>14.90147972106934</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>9.142857551574707</v>
-      </c>
-      <c r="B124" t="n">
-        <v>14.62510108947754</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>18</v>
-      </c>
-      <c r="B125" t="n">
-        <v>14.62404823303223</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>30.66666603088379</v>
-      </c>
-      <c r="B126" t="n">
-        <v>20.66903877258301</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>18.65079307556152</v>
-      </c>
-      <c r="B127" t="n">
-        <v>12.9657154083252</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>10.4761905670166</v>
-      </c>
-      <c r="B128" t="n">
-        <v>30.4447021484375</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>44.57143020629883</v>
-      </c>
-      <c r="B129" t="n">
-        <v>43.3536262512207</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>39.68254089355469</v>
-      </c>
-      <c r="B130" t="n">
-        <v>61.8558349609375</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>16.5714282989502</v>
-      </c>
-      <c r="B131" t="n">
-        <v>18.83149719238281</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>19.84127044677734</v>
-      </c>
-      <c r="B132" t="n">
-        <v>19.84765815734863</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>11.65524005889893</v>
-      </c>
-      <c r="B133" t="n">
-        <v>13.08944511413574</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>40.09523773193359</v>
-      </c>
-      <c r="B134" t="n">
-        <v>25.37488746643066</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>27.6785717010498</v>
-      </c>
-      <c r="B135" t="n">
-        <v>23.76729202270508</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>59.52381134033203</v>
-      </c>
-      <c r="B136" t="n">
-        <v>58.08315658569336</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>4.926108360290527</v>
-      </c>
-      <c r="B137" t="n">
-        <v>12.99399185180664</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>100</v>
-      </c>
-      <c r="B138" t="n">
-        <v>92.439453125</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>35.20000076293945</v>
-      </c>
-      <c r="B139" t="n">
-        <v>28.20357322692871</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>42.90000152587891</v>
-      </c>
-      <c r="B140" t="n">
-        <v>44.22418212890625</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>10.91269874572754</v>
-      </c>
-      <c r="B141" t="n">
-        <v>12.53678512573242</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>32.41919708251953</v>
-      </c>
-      <c r="B142" t="n">
-        <v>25.38352584838867</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>79.36508178710938</v>
-      </c>
-      <c r="B143" t="n">
-        <v>77.40055084228516</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>20</v>
-      </c>
-      <c r="B144" t="n">
-        <v>27.21893692016602</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>20</v>
-      </c>
-      <c r="B145" t="n">
-        <v>54.08646011352539</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>20.53571510314941</v>
-      </c>
-      <c r="B146" t="n">
-        <v>18.20253944396973</v>
+        <v>18.56622505187988</v>
       </c>
     </row>
   </sheetData>
